--- a/hermes/手动挑配置记录.xlsx
+++ b/hermes/手动挑配置记录.xlsx
@@ -12598,6 +12598,28 @@
           <t>Tier1</t>
         </is>
       </c>
+      <c r="D392" t="n">
+        <v>0.8778</v>
+      </c>
+      <c r="E392" t="n">
+        <v>20</v>
+      </c>
+      <c r="F392" t="n">
+        <v>5</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>0,10,10,10,0</t>
+        </is>
+      </c>
+      <c r="H392" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>用户确认入库；8-25多档位summary p0 summary 180局 early:threshold</t>
+        </is>
+      </c>
     </row>
     <row r="393" s="1">
       <c r="A393" t="n">
@@ -12608,6 +12630,24 @@
           <t>Tier2</t>
         </is>
       </c>
+      <c r="D393" t="n">
+        <v>0.8778</v>
+      </c>
+      <c r="E393" t="n">
+        <v>20</v>
+      </c>
+      <c r="F393" t="n">
+        <v>5</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>0,10,10,10,0</t>
+        </is>
+      </c>
+      <c r="H393" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I393" t="inlineStr"/>
     </row>
     <row r="394" s="1">
       <c r="A394" t="n">
@@ -12618,6 +12658,28 @@
           <t>Tier3</t>
         </is>
       </c>
+      <c r="D394" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E394" t="n">
+        <v>38</v>
+      </c>
+      <c r="F394" t="n">
+        <v>5</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>0,0,0,10,10</t>
+        </is>
+      </c>
+      <c r="H394" t="n">
+        <v>1</v>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>用户确认入库；8-25多档位summary p3 summary 320局 early:threshold</t>
+        </is>
+      </c>
     </row>
     <row r="395" s="1">
       <c r="A395" t="n">
@@ -12628,6 +12690,28 @@
           <t>Tier4</t>
         </is>
       </c>
+      <c r="D395" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E395" t="n">
+        <v>40</v>
+      </c>
+      <c r="F395" t="n">
+        <v>5</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>10,10,0,0,0</t>
+        </is>
+      </c>
+      <c r="H395" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>用户确认入库；8-25多档位summary p3 summary 400局 full</t>
+        </is>
+      </c>
     </row>
     <row r="396" s="1">
       <c r="A396" t="n">
@@ -12638,6 +12722,24 @@
           <t>Tier5</t>
         </is>
       </c>
+      <c r="D396" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E396" t="n">
+        <v>40</v>
+      </c>
+      <c r="F396" t="n">
+        <v>5</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>10,10,0,0,0</t>
+        </is>
+      </c>
+      <c r="H396" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I396" t="inlineStr"/>
     </row>
     <row r="397" s="1">
       <c r="A397" t="n">

--- a/hermes/手动挑配置记录.xlsx
+++ b/hermes/手动挑配置记录.xlsx
@@ -9424,21 +9424,26 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>0.64</v>
+        <v>0.6882</v>
       </c>
       <c r="E287" t="n">
         <v>20</v>
       </c>
       <c r="F287" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>1,1,1,10,10</t>
+          <t>0,10,10,10</t>
         </is>
       </c>
       <c r="H287" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>用户确认入库；auto_loop六轮累计池最优组合 bot 340局，created_at 2026-08-25T16:19:50</t>
+        </is>
       </c>
     </row>
     <row r="288" s="1">
@@ -9451,21 +9456,26 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>0.522</v>
+        <v>0.5425</v>
       </c>
       <c r="E288" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F288" t="n">
         <v>5</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>1,10,1,10,1</t>
+          <t>10,1,1,1,1</t>
         </is>
       </c>
       <c r="H288" t="n">
         <v>0.5</v>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>用户确认入库；auto_loop六轮累计池最优组合 bot 400局，created_at 2026-08-25T17:05:49</t>
+        </is>
       </c>
     </row>
     <row r="289" s="1">
@@ -9478,7 +9488,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>0.376</v>
+        <v>0.3974</v>
       </c>
       <c r="E289" t="n">
         <v>20</v>
@@ -9488,11 +9498,16 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>1,1,1,10,1</t>
+          <t>0,10,0,10,0</t>
         </is>
       </c>
       <c r="H289" t="n">
         <v>0.5</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>用户确认入库；auto_loop六轮累计池最优组合 bot 380局，created_at 2026-08-25T16:39:01</t>
+        </is>
       </c>
     </row>
     <row r="290" s="1">
@@ -9505,21 +9520,26 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>0.243</v>
+        <v>0.2875</v>
       </c>
       <c r="E290" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F290" t="n">
         <v>5</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>10,10,1,1,1</t>
+          <t>1,1,10,1,1</t>
         </is>
       </c>
       <c r="H290" t="n">
         <v>0.5</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>用户确认入库；auto_loop六轮累计池最优组合 bot 400局，created_at 2026-08-25T17:14:03</t>
+        </is>
       </c>
     </row>
     <row r="291" s="1">
@@ -9532,21 +9552,26 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>0.161</v>
+        <v>0.188</v>
       </c>
       <c r="E291" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F291" t="n">
         <v>5</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>10,10,1,1,1</t>
+          <t>0,0,0,0,10</t>
         </is>
       </c>
       <c r="H291" t="n">
         <v>0.5</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>用户确认入库；auto_loop六轮累计池最优组合 summary 250局，created_at 2026-08-25T00:41:41</t>
+        </is>
       </c>
     </row>
     <row r="292" s="1">
@@ -12647,7 +12672,6 @@
       <c r="H393" t="n">
         <v>0.5</v>
       </c>
-      <c r="I393" t="inlineStr"/>
     </row>
     <row r="394" s="1">
       <c r="A394" t="n">
@@ -12739,7 +12763,6 @@
       <c r="H396" t="n">
         <v>0.5</v>
       </c>
-      <c r="I396" t="inlineStr"/>
     </row>
     <row r="397" s="1">
       <c r="A397" t="n">
@@ -18945,6 +18968,28 @@
           <t>Tier1</t>
         </is>
       </c>
+      <c r="D597" t="n">
+        <v>0.8038</v>
+      </c>
+      <c r="E597" t="n">
+        <v>40</v>
+      </c>
+      <c r="F597" t="n">
+        <v>5</v>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>0,0,0,0,10</t>
+        </is>
+      </c>
+      <c r="H597" t="n">
+        <v>1</v>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>用户确认入库；8-25改关卡后多档位summary p3 summary 260局 early:threshold</t>
+        </is>
+      </c>
     </row>
     <row r="598" s="1">
       <c r="A598" t="n">
@@ -18955,6 +19000,23 @@
           <t>Tier2</t>
         </is>
       </c>
+      <c r="D598" t="n">
+        <v>0.8038</v>
+      </c>
+      <c r="E598" t="n">
+        <v>40</v>
+      </c>
+      <c r="F598" t="n">
+        <v>5</v>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>0,0,0,0,10</t>
+        </is>
+      </c>
+      <c r="H598" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="599" s="1">
       <c r="A599" t="n">
@@ -18965,6 +19027,28 @@
           <t>Tier3</t>
         </is>
       </c>
+      <c r="D599" t="n">
+        <v>0.5846</v>
+      </c>
+      <c r="E599" t="n">
+        <v>31</v>
+      </c>
+      <c r="F599" t="n">
+        <v>3</v>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>1,1,4</t>
+        </is>
+      </c>
+      <c r="H599" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>用户确认入库；8-25改关卡后多档位summary p0 summary 390局 early:threshold</t>
+        </is>
+      </c>
     </row>
     <row r="600" s="1">
       <c r="A600" t="n">
@@ -18975,6 +19059,28 @@
           <t>Tier4</t>
         </is>
       </c>
+      <c r="D600" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="E600" t="n">
+        <v>40</v>
+      </c>
+      <c r="F600" t="n">
+        <v>5</v>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>0,0,9,0,0</t>
+        </is>
+      </c>
+      <c r="H600" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>用户确认入库；8-25改关卡后多档位summary p3 summary 400局 full</t>
+        </is>
+      </c>
     </row>
     <row r="601" s="1">
       <c r="A601" t="n">
@@ -18984,6 +19090,23 @@
         <is>
           <t>Tier5</t>
         </is>
+      </c>
+      <c r="D601" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="E601" t="n">
+        <v>40</v>
+      </c>
+      <c r="F601" t="n">
+        <v>5</v>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>0,0,9,0,0</t>
+        </is>
+      </c>
+      <c r="H601" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="602" s="1">
